--- a/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,72</t>
+          <t>0,08; 0,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -943,27 +943,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,22</t>
+          <t>-0,72; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,25</t>
+          <t>-0,72; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,0</t>
+          <t>-2,14; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,4</t>
+          <t>-0,97; 0,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,6</t>
+          <t>-0,27; 0,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,52</t>
+          <t>-0,29; 0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,54</t>
+          <t>-0,1; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,51; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,46</t>
+          <t>-0,12; 0,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,25</t>
+          <t>-0,22; 0,24</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 985,83</t>
+          <t>-77,45; 1124,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,72</t>
+          <t>-1,09; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-1,98; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,68</t>
+          <t>0,07; 0,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,51</t>
         </is>
       </c>
     </row>
@@ -943,22 +943,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,2</t>
+          <t>-0,72; 1,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,63</t>
+          <t>-0,72; 1,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,0</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,39</t>
+          <t>-0,99; 0,39</t>
         </is>
       </c>
     </row>
@@ -1104,27 +1104,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,52</t>
+          <t>-0,27; 0,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,61</t>
+          <t>-0,1; 0,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,0</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 0,43</t>
+          <t>-0,09; 0,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,24</t>
+          <t>-0,19; 0,25</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-77,45; 1124,24</t>
+          <t>-66,75; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,72</t>
+          <t>-1,1; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,0</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,78</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,46</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,05</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,26</t>
+          <t>-2,61; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>-1,73; 0,0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-0,72; 1,22</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>-0,72; 1,25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 0,0</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>-0,96; 0,4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>-0,97; 0,39</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,99; 0,39</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>11,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>14,28%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,6</t>
+          <t>-0,11; 0,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,56</t>
+          <t>-0,47; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,54</t>
+          <t>-0,26; 0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,27; 0,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,42</t>
+          <t>-0,09; 0,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,25</t>
+          <t>-0,2; 0,25</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>183,94%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>58,24%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>58,61%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>183,94%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,75; —</t>
+          <t>-75,17; 985,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1013-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,384 +600,236 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7463861529527505</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.005711520118231814</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3611367944421326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,72</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 0,72</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,82; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-4.606213835576606</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.554580446855186</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.098190977139006</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.824948754202622</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.72340731403456</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.7155974603441742</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.01581539241121832</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,96</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,95</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,08; 0,72</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,46</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2752795030694357</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3147595671401232</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.289669726584426</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.2941247525758168</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.142356478974884</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.07716376172665032</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9642066973132919</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr"/>
+      <c r="E12" s="5" t="n">
+        <v>1.100984699221725</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.9468835938396742</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.7197338173499259</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.459524754999955</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,73; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 1,22</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,72; 1,25</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,96; 0,4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,97; 0,39</t>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -976,82 +837,34 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-49,7%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-49,77%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +872,273 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.4256821102391004</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4256821102391004</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04218417298070772</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.05103237971506532</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.1938026282715727</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.1940764855461892</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,11; 0,54</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,0</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,26; 0,6</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,27; 0,52</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,09; 0,46</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,2; 0,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.607271813568509</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.727857627457533</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.7177557428522998</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-0.7198804235227891</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.9625775372394921</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.973120178316555</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>183,94%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>58,24%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>58,61%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>101,94%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.224246187834406</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.246262205998754</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.3959647351146647</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.3942294581228416</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-75,17; 985,83</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.1180165525591216</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.1427707383433695</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4970234057421755</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.4977257361312476</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.1715078642818037</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.09323976379685353</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1080961843335051</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.1087808647730914</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.1407462183180349</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.005007856897554404</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.1134698494761462</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.4666431535668149</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.258758792263909</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.2688536913228948</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.09476209234545631</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.1965250600093373</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.5417902733761943</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.596622048172204</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.5175032925787235</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.4630273885175636</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.2503929709204795</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>1.839428343635416</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.582417089577478</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.5861061151557001</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1.019371567655375</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.03627001135276466</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.75173157111314</v>
+      </c>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>9.858267044961234</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1146,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
